--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:46</t>
+    <t xml:space="preserve">2026-09-09 23:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:46</t>
+    <t xml:space="preserve">2026-09-18 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:35</t>
+    <t xml:space="preserve">2026-09-23 13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:07</t>
+    <t xml:space="preserve">2026-10-02 15:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:43</t>
+    <t xml:space="preserve">2026-10-05 13:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>145050.62</v>
+        <v>145050.63</v>
       </c>
     </row>
     <row r="3">
